--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -439,27 +439,27 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>classe_T1</t>
+          <t>Y_T1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>classe_T2</t>
+          <t>Y_T2</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>classe_T3</t>
+          <t>Y_T3</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>classe_T4</t>
+          <t>Y_T4</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>classe_T5</t>
+          <t>Y_T5</t>
         </is>
       </c>
     </row>
@@ -476,30 +476,20 @@
       <c r="D2" t="n">
         <v>5.9891</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
+      <c r="E2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +505,20 @@
       <c r="D3" t="n">
         <v>5.5912</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -554,30 +534,20 @@
       <c r="D4" t="n">
         <v>5.8234</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -593,30 +563,20 @@
       <c r="D5" t="n">
         <v>8.0677</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -632,30 +592,20 @@
       <c r="D6" t="n">
         <v>6.304</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -671,30 +621,20 @@
       <c r="D7" t="n">
         <v>3.6005</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -710,30 +650,20 @@
       <c r="D8" t="n">
         <v>6.1537</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
+      <c r="E8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -749,30 +679,20 @@
       <c r="D9" t="n">
         <v>4.4058</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -788,30 +708,20 @@
       <c r="D10" t="n">
         <v>4.9263</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
+      <c r="E10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -827,30 +737,20 @@
       <c r="D11" t="n">
         <v>1.2548</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
+      <c r="E11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/validacao.xlsx
+++ b/datasets/validacao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Y_T1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Y_T2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Y_T3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Y_T4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Y_T5</t>
         </is>
@@ -489,6 +494,9 @@
         <v>-1</v>
       </c>
       <c r="I2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J2" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -520,6 +528,9 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -549,6 +560,9 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -578,6 +592,9 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -607,6 +624,9 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -636,6 +656,9 @@
       <c r="I7" t="n">
         <v>1</v>
       </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -665,6 +688,9 @@
       <c r="I8" t="n">
         <v>-1</v>
       </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -694,6 +720,9 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -723,6 +752,9 @@
       <c r="I10" t="n">
         <v>-1</v>
       </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -750,6 +782,9 @@
         <v>-1</v>
       </c>
       <c r="I11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" t="n">
         <v>-1</v>
       </c>
     </row>
